--- a/fhir/ig/laboratorio/v0.1.0/StructureDefinition-ResultadoDiagnosticoLaboratorio.xlsx
+++ b/fhir/ig/laboratorio/v0.1.0/StructureDefinition-ResultadoDiagnosticoLaboratorio.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:13:46-03:00</t>
+    <t>2026-09-15T10:16:15-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -527,7 +527,7 @@
     <t>Details concerning a service requested.</t>
   </si>
   <si>
-    <t>Note: Usually there is one test request for each result, however in some circumstances multiple test requests may be represented using a single test result resource. Note that there are also cases where one request leads to multiple reports.</t>
+    <t>En esta fase, el laboratorio puede emitir un resultado sin una solicitud (`ServiceRequest`) previa registrada en el Bus, cuando el examen se originó y procesó completamente en el sistema del propio laboratorio (ver Casos de uso, Alcance por fases). Cuando exista una solicitud registrada, se recomienda referenciarla mediante `basedOn`.</t>
   </si>
   <si>
     <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>79</v>

--- a/fhir/ig/laboratorio/v0.1.0/StructureDefinition-ResultadoDiagnosticoLaboratorio.xlsx
+++ b/fhir/ig/laboratorio/v0.1.0/StructureDefinition-ResultadoDiagnosticoLaboratorio.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T10:16:15-03:00</t>
+    <t>2026-09-21T17:12:23-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -952,7 +952,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1)
+    <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/laboratorio/StructureDefinition/MinsalObservacionLaboratorio)
 </t>
   </si>
   <si>
@@ -962,7 +962,7 @@
     <t>[Observations](http://hl7.org/fhir/R4/observation.html)  that are part of this diagnostic report.</t>
   </si>
   <si>
-    <t>Observations can contain observations.</t>
+    <t>Referencia al resultado atómico por analito (Caso de uso 3), cuando el establecimiento lo informa además del PDF. Cada instancia de MinsalObservacionLaboratorio referencia a su vez, mediante basedOn, la ServiceRequest específica de su prestación.</t>
   </si>
   <si>
     <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>

--- a/fhir/ig/laboratorio/v0.1.0/StructureDefinition-ResultadoDiagnosticoLaboratorio.xlsx
+++ b/fhir/ig/laboratorio/v0.1.0/StructureDefinition-ResultadoDiagnosticoLaboratorio.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.5.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T17:12:23-03:00</t>
+    <t>2026-09-22T09:29:02-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
